--- a/data/processed/missing_data_report.xlsx
+++ b/data/processed/missing_data_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,21 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Pct</t>
         </is>
@@ -461,79 +449,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>int_bandwidth_i994</t>
+          <t>mobile_broad_price_ppp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="C3" t="n">
-        <v>31.7</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>int_bandwidth_i4214</t>
+          <t>mobile_broad_price_usd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157</v>
+        <v>264</v>
       </c>
       <c r="C4" t="n">
-        <v>31.7</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>int_bandwidth_i994u</t>
+          <t>mobile_broad_price_gni_pct</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>157</v>
+        <v>264</v>
       </c>
       <c r="C5" t="n">
-        <v>31.7</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mobile_broad_price_ppp</t>
+          <t>int_bandwidth_i994</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mobile_broad_price_gni_pct</t>
+          <t>int_bandwidth_i994u</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>20.4</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mobile_broad_price_usd</t>
+          <t>int_bandwidth_i4214</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="C8" t="n">
-        <v>20.4</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="9">
@@ -604,20 +592,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wage_salaried_workers</t>
+          <t>regulatory_quality_estimate</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>access_to_electricity</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -630,7 +618,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>regulatory_quality_estimate</t>
+          <t>access_to_electricity</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -643,27 +631,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>labor_force_advanced_education</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>labor_force_advanced_education</t>
+          <t>fixed_broad_price_ppp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>6.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">
@@ -673,42 +661,42 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>internet_users_pct_i99H</t>
+          <t>mobile_subs_i911</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fixed_broad_price_ppp</t>
+          <t>mobile_subs_i271</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mobile_subs_i911</t>
+          <t>wage_salaried_workers</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -721,14 +709,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mobile_subs_i271</t>
+          <t>fixed_broadband_subs_i992b</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24">
@@ -741,6 +729,19 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fixed_broadband_subs_i4213tfbb</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
         <v>0.2</v>
       </c>
     </row>
